--- a/Total_rows.xlsx
+++ b/Total_rows.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\Vibe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{999BE8D9-6657-4A26-AA92-3BC128FCFCFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83EACC19-3496-4B66-936E-8899E1E021EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1420" yWindow="2620" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -363,7 +363,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.54296875" bestFit="1" customWidth="1"/>
@@ -398,6 +398,21 @@
         <v>240</v>
       </c>
     </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>208</v>
+      </c>
+      <c r="C3">
+        <v>43</v>
+      </c>
+      <c r="D3">
+        <f>D2+B3-C3</f>
+        <v>405</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Total_rows.xlsx
+++ b/Total_rows.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\Vibe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83EACC19-3496-4B66-936E-8899E1E021EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32B60263-F2BE-4A64-8ADC-F8FA5DF1BF94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1420" yWindow="2620" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -363,7 +363,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.54296875" bestFit="1" customWidth="1"/>
@@ -413,6 +413,21 @@
         <v>405</v>
       </c>
     </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>136</v>
+      </c>
+      <c r="C4">
+        <v>7</v>
+      </c>
+      <c r="D4">
+        <f>D3+B4-C4</f>
+        <v>534</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Total_rows.xlsx
+++ b/Total_rows.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\Vibe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32B60263-F2BE-4A64-8ADC-F8FA5DF1BF94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F72573D-862C-4969-A6E2-C9DE97A0AC7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1420" yWindow="2620" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -363,7 +363,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.54296875" bestFit="1" customWidth="1"/>
@@ -428,6 +428,21 @@
         <v>534</v>
       </c>
     </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>174</v>
+      </c>
+      <c r="C5">
+        <v>30</v>
+      </c>
+      <c r="D5">
+        <f>D4+B5-C5</f>
+        <v>678</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Total_rows.xlsx
+++ b/Total_rows.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\Vibe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F72573D-862C-4969-A6E2-C9DE97A0AC7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84F9D45D-A01E-4DA3-9306-17E2B4C7AA6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1420" yWindow="2620" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -363,7 +363,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.54296875" bestFit="1" customWidth="1"/>
@@ -443,6 +443,21 @@
         <v>678</v>
       </c>
     </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>104</v>
+      </c>
+      <c r="C6">
+        <v>46</v>
+      </c>
+      <c r="D6">
+        <f>D5+B6-C6</f>
+        <v>736</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
